--- a/administrative_forms/002_international_student_application_form--administrative_forms.xlsx
+++ b/administrative_forms/002_international_student_application_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'course_1'}</t>
+          <t>course_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Course 1'}</t>
+          <t>Course 1</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'course_2'}</t>
+          <t>course_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Course 2'}</t>
+          <t>Course 2</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'course_3'}</t>
+          <t>course_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Course 3'}</t>
+          <t>Course 3</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'uk'}</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'UK'}</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'india'}</t>
+          <t>india</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'India'}</t>
+          <t>India</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'heart_condition'}</t>
+          <t>heart_condition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Heart Condition'}</t>
+          <t>Heart Condition</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'paracetamol'}</t>
+          <t>paracetamol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Paracetamol'}</t>
+          <t>Paracetamol</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'passport'}</t>
+          <t>passport</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Passport'}</t>
+          <t>Passport</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'visa'}</t>
+          <t>visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Visa'}</t>
+          <t>Visa</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'id_card'}</t>
+          <t>id_card</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'ID Card'}</t>
+          <t>ID Card</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
